--- a/assets/constructions/examples/ctd_eths_holder_drill.xlsx
+++ b/assets/constructions/examples/ctd_eths_holder_drill.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD6"/>
+  <dimension ref="A1:AH6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,6 +577,26 @@
       <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>releasepack</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
         </is>
       </c>
     </row>
@@ -673,11 +693,17 @@
           <t>2018/!Likon_Инструментальный каталог_2018.pdf</t>
         </is>
       </c>
+      <c r="AE2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E1-30-32</t>
+          <t>E1-30-40</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -704,12 +730,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ISO_9766:32</t>
+          <t>ISO_9766:40</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>LIK_E1-32</t>
+          <t>LIK_E1-40</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -718,7 +744,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -739,7 +765,7 @@
         <v>30</v>
       </c>
       <c r="R3" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="n">
@@ -767,11 +793,17 @@
           <t>2018/!Likon_Инструментальный каталог_2018.pdf</t>
         </is>
       </c>
+      <c r="AE3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E1-30-25</t>
+          <t>E1-30-32</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -798,12 +830,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ISO_9766:25</t>
+          <t>ISO_9766:32</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>LIK_E1-25</t>
+          <t>LIK_E1-32</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -812,7 +844,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -833,7 +865,7 @@
         <v>30</v>
       </c>
       <c r="R4" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="n">
@@ -861,11 +893,17 @@
           <t>2018/!Likon_Инструментальный каталог_2018.pdf</t>
         </is>
       </c>
+      <c r="AE4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E1-30-40</t>
+          <t>E1-30-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -892,12 +930,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ISO_9766:40</t>
+          <t>ISO_9766:16</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>LIK_E1-40</t>
+          <t>LIK_E1-16</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -906,7 +944,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -927,7 +965,7 @@
         <v>30</v>
       </c>
       <c r="R5" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="n">
@@ -955,11 +993,17 @@
           <t>2018/!Likon_Инструментальный каталог_2018.pdf</t>
         </is>
       </c>
+      <c r="AE5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E1-30-16</t>
+          <t>E1-30-25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -986,12 +1030,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ISO_9766:16</t>
+          <t>ISO_9766:25</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>LIK_E1-16</t>
+          <t>LIK_E1-25</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1000,7 +1044,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -1021,7 +1065,7 @@
         <v>30</v>
       </c>
       <c r="R6" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="n">
@@ -1049,6 +1093,12 @@
           <t>2018/!Likon_Инструментальный каталог_2018.pdf</t>
         </is>
       </c>
+      <c r="AE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
